--- a/originales/respuestas/2025/01. Calificadas/bucle p11/Secretaría Distrital De Cultura, Recreación Y Deporte.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p11/Secretaría Distrital De Cultura, Recreación Y Deporte.xlsx
@@ -16,7 +16,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="71">
+  <si>
+    <t>Entidad</t>
+  </si>
   <si>
     <t>Tipo</t>
   </si>
@@ -346,7 +349,7 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -586,101 +589,103 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="4">
         <v>0.0</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" s="4">
         <v>5.0</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="4">
         <v>5.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="4">
         <v>5.0</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" s="5">
         <v>1.0</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P2" s="4">
         <v>5.0</v>
@@ -689,49 +694,49 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="4">
         <v>0.0</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="4">
         <v>5.0</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" s="4">
         <v>5.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L3" s="4">
         <v>5.0</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N3" s="5">
         <v>1.0</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="4">
         <v>5.0</v>
@@ -740,49 +745,49 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="4">
         <v>1.15832175E8</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="4">
         <v>5.0</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J4" s="4">
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" s="4">
         <v>5.0</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N4" s="4">
         <v>5.0</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P4" s="4">
         <v>5.0</v>
@@ -791,49 +796,49 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" s="4">
         <v>1.2244759E8</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" s="4">
         <v>5.0</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" s="4">
         <v>5.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" s="4">
         <v>5.0</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N5" s="4">
         <v>5.0</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P5" s="4">
         <v>5.0</v>
@@ -842,49 +847,49 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="4">
         <v>2.5E8</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6" s="4">
         <v>5.0</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" s="4">
         <v>5.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L6" s="4">
         <v>5.0</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N6" s="4">
         <v>5.0</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P6" s="4">
         <v>5.0</v>
@@ -893,49 +898,49 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7" s="4">
         <v>1.31216023E8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" s="4">
         <v>5.0</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J7" s="4">
         <v>5.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="4">
         <v>5.0</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N7" s="4">
         <v>5.0</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P7" s="4">
         <v>5.0</v>
@@ -944,49 +949,49 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E8" s="4">
         <v>2651850.0</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H8" s="5">
         <v>5.0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8" s="4">
         <v>5.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L8" s="4">
         <v>5.0</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N8" s="4">
         <v>5.0</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P8" s="4">
         <v>5.0</v>
@@ -995,49 +1000,49 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E9" s="4">
         <v>1.41E7</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H9" s="5">
         <v>5.0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J9" s="4">
         <v>5.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L9" s="4">
         <v>5.0</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N9" s="4">
         <v>5.0</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P9" s="4">
         <v>5.0</v>
@@ -1046,47 +1051,47 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" s="4">
         <v>5200000.0</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H10" s="5">
         <v>1.0</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="4">
         <v>5.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L10" s="4">
         <v>5.0</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N10" s="4">
         <v>5.0</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P10" s="4">
         <v>5.0</v>
@@ -1095,47 +1100,47 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11" s="4">
         <v>9.5E7</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H11" s="5">
         <v>1.0</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J11" s="4">
         <v>5.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L11" s="4">
         <v>5.0</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N11" s="4">
         <v>5.0</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P11" s="4">
         <v>5.0</v>
@@ -1144,47 +1149,47 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E12" s="4">
         <v>1.4E7</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H12" s="5">
         <v>1.0</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J12" s="4">
         <v>5.0</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L12" s="4">
         <v>5.0</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N12" s="4">
         <v>5.0</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P12" s="4">
         <v>5.0</v>
@@ -1193,47 +1198,47 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13" s="4">
         <v>4.5E7</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H13" s="5">
         <v>1.0</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J13" s="4">
         <v>5.0</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L13" s="4">
         <v>5.0</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N13" s="4">
         <v>5.0</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P13" s="4">
         <v>5.0</v>
@@ -1242,47 +1247,47 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14" s="4">
         <v>1.5E7</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H14" s="5">
         <v>1.0</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J14" s="4">
         <v>5.0</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L14" s="4">
         <v>5.0</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N14" s="4">
         <v>5.0</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P14" s="4">
         <v>5.0</v>
@@ -1291,43 +1296,43 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H15" s="5">
         <v>1.0</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J15" s="4">
         <v>5.0</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L15" s="4">
         <v>5.0</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N15" s="5">
         <v>1.0</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P15" s="5">
         <v>1.0</v>
@@ -1336,41 +1341,41 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H16" s="5">
         <v>1.0</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J16" s="4">
         <v>5.0</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L16" s="4">
         <v>5.0</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N16" s="5">
         <v>1.0</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P16" s="5">
         <v>1.0</v>
